--- a/medical_surveys_questionnaires/041_injection_therapy_intake_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/041_injection_therapy_intake_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medication_allergies</t>
+          <t>medication_allergies_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medication Allergies</t>
+          <t>Medication Allergies 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Medical Conditions 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>consent</t>
+          <t>consent_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Consent</t>
+          <t>Consent 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'yes'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Yes'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'no'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'No'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'yes'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'Yes'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'no'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'No'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'yes'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Yes'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'no'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'No'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'yes'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Yes'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1318,53 +1318,53 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'no'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'No'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>medication_allergies_choices</t>
+          <t>medication_allergies_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'yes'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Yes'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>medication_allergies_choices</t>
+          <t>medication_allergies_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'no'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'No'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>consent_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>consent_choices</t>
+          <t>consent_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
